--- a/files/九龙-启德-Monaco One.xlsx
+++ b/files/九龙-启德-Monaco One.xlsx
@@ -26424,7 +26424,7 @@
         </is>
       </c>
       <c r="E417" s="4" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>8474000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>25757</v>
+        <v>25835</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>8474000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>25757</v>
+        <v>25835</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -35244,9 +35244,9 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>F | 329呎 (1房)
+          <t>F | 328呎 (1房)
 $847万
-$25,757/呎
+$25,835/呎
 (21年-12月-17日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco One.xlsx
+++ b/files/九龙-启德-Monaco One.xlsx
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>11779000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>26470</v>
+        <v>26410</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>11779000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>26470</v>
+        <v>26410</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -31553,9 +31553,9 @@
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>E | 445呎 (2房)
+          <t>E | 446呎 (2房)
 $1178万
-$26,470/呎
+$26,410/呎
 (21年-12月-15日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Monaco One.xlsx
+++ b/files/九龙-启德-Monaco One.xlsx
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>8129000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>8129000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>11477000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>25733</v>
+        <v>25791</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>11477000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25733</v>
+        <v>25791</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>8073000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>8073000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>10558000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>23726</v>
+        <v>23779</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>10558000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>23726</v>
+        <v>23779</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>11779000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>26410</v>
+        <v>26470</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>11779000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>26410</v>
+        <v>26470</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>10495000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>23584</v>
+        <v>23637</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>10495000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23584</v>
+        <v>23637</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>10495000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>23584</v>
+        <v>23637</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>10495000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>23584</v>
+        <v>23637</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>11385000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>25527</v>
+        <v>25584</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>11385000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>25527</v>
+        <v>25584</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>8008000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>25025</v>
+        <v>25103</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>8008000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>25025</v>
+        <v>25103</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>10464000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>23515</v>
+        <v>23568</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>10464000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>23515</v>
+        <v>23568</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>11362000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>25475</v>
+        <v>25533</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>11362000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>25475</v>
+        <v>25533</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>10728000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>24108</v>
+        <v>24162</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>10728000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>24108</v>
+        <v>24162</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>11662000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>26148</v>
+        <v>26207</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>11662000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>26148</v>
+        <v>26207</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>10724000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>24099</v>
+        <v>24153</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>10724000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>24099</v>
+        <v>24153</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>11294000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>25323</v>
+        <v>25380</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>11294000</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>25323</v>
+        <v>25380</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>8122000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>25381</v>
+        <v>25461</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>8122000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>25381</v>
+        <v>25461</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>11225000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>25168</v>
+        <v>25225</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>11225000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>25168</v>
+        <v>25225</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>11197000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>25105</v>
+        <v>25162</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>11197000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>25105</v>
+        <v>25162</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>10216000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>22957</v>
+        <v>23009</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>10216000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>22957</v>
+        <v>23009</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>10475000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>23539</v>
+        <v>23592</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>10475000</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>23539</v>
+        <v>23592</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>11141000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>24980</v>
+        <v>25036</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>11141000</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>24980</v>
+        <v>25036</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>10443000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>23467</v>
+        <v>23520</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>10443000</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>23467</v>
+        <v>23520</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>11303000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>25343</v>
+        <v>25400</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>11303000</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>25343</v>
+        <v>25400</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>10125000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>22753</v>
+        <v>22804</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>10125000</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>22753</v>
+        <v>22804</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>10381000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>23328</v>
+        <v>23381</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>10381000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>23328</v>
+        <v>23381</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>7961000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>24878</v>
+        <v>24956</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>7961000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>24878</v>
+        <v>24956</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>10034000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>22548</v>
+        <v>22599</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>10034000</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>22548</v>
+        <v>22599</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>11003000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>24670</v>
+        <v>24726</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>11003000</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>24670</v>
+        <v>24726</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>11253000</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>25231</v>
+        <v>25288</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>11253000</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>25231</v>
+        <v>25288</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>11225000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>25168</v>
+        <v>25225</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>11225000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>25168</v>
+        <v>25225</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>9885000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>22213</v>
+        <v>22264</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>9885000</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>22213</v>
+        <v>22264</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>10843000</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>24312</v>
+        <v>24366</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>10843000</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>24312</v>
+        <v>24366</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>9856000</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>22148</v>
+        <v>22198</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>9856000</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>22148</v>
+        <v>22198</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>7855000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>24547</v>
+        <v>24624</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>7855000</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>24547</v>
+        <v>24624</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>7847000</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>24522</v>
+        <v>24599</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>7847000</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>24522</v>
+        <v>24599</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>9797000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>22016</v>
+        <v>22065</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>9797000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>22016</v>
+        <v>22065</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>11018000</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>24704</v>
+        <v>24760</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>11018000</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>24704</v>
+        <v>24760</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>7807000</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>24397</v>
+        <v>24473</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>7807000</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>24397</v>
+        <v>24473</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>10952000</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>24556</v>
+        <v>24611</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>10952000</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>24556</v>
+        <v>24611</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>7800000</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>24375</v>
+        <v>24451</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>7800000</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>24375</v>
+        <v>24451</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>7792000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>24350</v>
+        <v>24426</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>7792000</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>24350</v>
+        <v>24426</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>10947000</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>24545</v>
+        <v>24600</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>10947000</v>
       </c>
       <c r="L236" s="5" t="n">
-        <v>24545</v>
+        <v>24600</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>7783000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>24322</v>
+        <v>24398</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>7783000</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>24322</v>
+        <v>24398</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>10012000</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>22499</v>
+        <v>22550</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>10012000</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>22499</v>
+        <v>22550</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>8469000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>26466</v>
+        <v>26549</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>8469000</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>26466</v>
+        <v>26549</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         </is>
       </c>
       <c r="E252" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>9061000</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>27625</v>
+        <v>27541</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>9061000</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>27625</v>
+        <v>27541</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>8419000</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>26309</v>
+        <v>26392</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>8419000</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>26309</v>
+        <v>26392</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>8758000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>26701</v>
+        <v>26620</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>8758000</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>26701</v>
+        <v>26620</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>8162000</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>25506</v>
+        <v>25586</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>8162000</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>25506</v>
+        <v>25586</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>8980000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>27378</v>
+        <v>27295</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>8980000</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>27378</v>
+        <v>27295</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>8706000</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>26543</v>
+        <v>26462</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>8706000</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>26543</v>
+        <v>26462</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>8954000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>27299</v>
+        <v>27216</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>8954000</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>27299</v>
+        <v>27216</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>8680000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>26463</v>
+        <v>26383</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>8680000</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>26463</v>
+        <v>26383</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="E287" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>8073000</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>8073000</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>8654000</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>26384</v>
+        <v>26304</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>8654000</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>26384</v>
+        <v>26304</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>8654000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>26384</v>
+        <v>26304</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>8654000</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>26384</v>
+        <v>26304</v>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         </is>
       </c>
       <c r="E297" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>8873000</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>27052</v>
+        <v>26970</v>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>8873000</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>27052</v>
+        <v>26970</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="E313" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>8821000</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>26893</v>
+        <v>26812</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>8821000</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>26893</v>
+        <v>26812</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>8220000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>25688</v>
+        <v>25768</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>8220000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>25688</v>
+        <v>25768</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         </is>
       </c>
       <c r="E327" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>8154000</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>25481</v>
+        <v>25561</v>
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>8154000</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>25481</v>
+        <v>25561</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>8763000</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>26716</v>
+        <v>26635</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>8763000</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>26716</v>
+        <v>26635</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>8129000</v>
       </c>
       <c r="I335" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>8129000</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>25403</v>
+        <v>25483</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>7882000</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>24631</v>
+        <v>24708</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>7882000</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>24631</v>
+        <v>24708</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>8444000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>25744</v>
+        <v>25666</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>8444000</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>25744</v>
+        <v>25666</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         </is>
       </c>
       <c r="E359" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>8073000</v>
       </c>
       <c r="I359" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>8073000</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>25228</v>
+        <v>25307</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>7803000</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>24384</v>
+        <v>24461</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>7803000</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>24384</v>
+        <v>24461</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>8368000</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>25512</v>
+        <v>25435</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>8368000</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>25512</v>
+        <v>25435</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>8344000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>25439</v>
+        <v>25362</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>8344000</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>25439</v>
+        <v>25362</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>8555000</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>26082</v>
+        <v>26003</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>8555000</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>26082</v>
+        <v>26003</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         </is>
       </c>
       <c r="E399" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>7914000</v>
       </c>
       <c r="I399" s="5" t="n">
-        <v>24731</v>
+        <v>24809</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>7914000</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>24731</v>
+        <v>24809</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         </is>
       </c>
       <c r="E407" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>7889000</v>
       </c>
       <c r="I407" s="5" t="n">
-        <v>24653</v>
+        <v>24730</v>
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>7889000</v>
       </c>
       <c r="L407" s="5" t="n">
-        <v>24653</v>
+        <v>24730</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         </is>
       </c>
       <c r="E417" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>8474000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>25835</v>
+        <v>25757</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>8474000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>25835</v>
+        <v>25757</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="E426" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
@@ -26998,7 +26998,7 @@
         <v>8589000</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>26186</v>
+        <v>26106</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>8589000</v>
       </c>
       <c r="L426" s="5" t="n">
-        <v>26186</v>
+        <v>26106</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="E434" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>8423000</v>
       </c>
       <c r="I434" s="5" t="n">
-        <v>25680</v>
+        <v>25602</v>
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>8423000</v>
       </c>
       <c r="L434" s="5" t="n">
-        <v>25680</v>
+        <v>25602</v>
       </c>
       <c r="M434" s="3" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>8373000</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>25527</v>
+        <v>25450</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>8373000</v>
       </c>
       <c r="L450" s="5" t="n">
-        <v>25527</v>
+        <v>25450</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>8298000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>25299</v>
+        <v>25222</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>8298000</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>25299</v>
+        <v>25222</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         </is>
       </c>
       <c r="E473" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>8273000</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>25223</v>
+        <v>25146</v>
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>8273000</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>25223</v>
+        <v>25146</v>
       </c>
       <c r="M473" s="3" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         </is>
       </c>
       <c r="E479" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>7580000</v>
       </c>
       <c r="I479" s="5" t="n">
-        <v>23688</v>
+        <v>23762</v>
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>7580000</v>
       </c>
       <c r="L479" s="5" t="n">
-        <v>23688</v>
+        <v>23762</v>
       </c>
       <c r="M479" s="3" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         </is>
       </c>
       <c r="E481" s="4" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>8249000</v>
       </c>
       <c r="I481" s="5" t="n">
-        <v>25149</v>
+        <v>25073</v>
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>8249000</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>25149</v>
+        <v>25073</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="E487" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>7787000</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>24334</v>
+        <v>24411</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>7787000</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>24334</v>
+        <v>24411</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
@@ -31427,9 +31427,9 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $813万
-$25,403/呎
+$25,483/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -31482,9 +31482,9 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1148万
-$25,733/呎
+$25,791/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -31553,25 +31553,25 @@
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1178万
-$26,410/呎
+$26,470/呎
 (21年-12月-15日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1056万
-$23,726/呎
+$23,779/呎
 (21年-12月-08日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $807万
-$25,228/呎
+$25,307/呎
 (21年-11月-13日)</t>
         </is>
       </c>
@@ -31703,9 +31703,9 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1050万
-$23,584/呎
+$23,637/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -31766,17 +31766,17 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1138万
-$25,527/呎
+$25,584/呎
 (21年-12月-14日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1050万
-$23,584/呎
+$23,637/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -31837,25 +31837,25 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1136万
-$25,475/呎
+$25,533/呎
 (21年-12月-16日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1046万
-$23,515/呎
+$23,568/呎
 (21年-12月-03日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $801万
-$25,025/呎
+$25,103/呎
 (21年-12月-03日)</t>
         </is>
       </c>
@@ -31908,17 +31908,17 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1166万
-$26,148/呎
+$26,207/呎
 (21年-12月-14日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1073万
-$24,108/呎
+$24,162/呎
 (21年-11月-13日)</t>
         </is>
       </c>
@@ -31987,9 +31987,9 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1072万
-$24,099/呎
+$24,153/呎
 (21年-12月-03日)</t>
         </is>
       </c>
@@ -32050,9 +32050,9 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1129万
-$25,323/呎
+$25,380/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -32121,9 +32121,9 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1122万
-$25,168/呎
+$25,225/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -32137,9 +32137,9 @@
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $812万
-$25,381/呎
+$25,461/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -32192,9 +32192,9 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1120万
-$25,105/呎
+$25,162/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -32271,9 +32271,9 @@
       </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1022万
-$22,957/呎
+$23,009/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -32334,17 +32334,17 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1114万
-$24,980/呎
+$25,036/呎
 (21年-12月-14日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1048万
-$23,539/呎
+$23,592/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -32405,17 +32405,17 @@
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1130万
-$25,343/呎
+$25,400/呎
 (21年-11月-18日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1044万
-$23,467/呎
+$23,520/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -32484,9 +32484,9 @@
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1012万
-$22,753/呎
+$22,804/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -32555,9 +32555,9 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1038万
-$23,328/呎
+$23,381/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -32689,25 +32689,25 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1100万
-$24,670/呎
+$24,726/呎
 (21年-11月-18日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1003万
-$22,548/呎
+$22,599/呎
 (21年-12月-08日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $796万
-$24,878/呎
+$24,956/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -32760,9 +32760,9 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1125万
-$25,231/呎
+$25,288/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -32831,9 +32831,9 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1122万
-$25,168/呎
+$25,225/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -32973,17 +32973,17 @@
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1084万
-$24,312/呎
+$24,366/呎
 (21年-12月-09日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $988万
-$22,213/呎
+$22,264/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -33052,9 +33052,9 @@
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $986万
-$22,148/呎
+$22,198/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -33131,9 +33131,9 @@
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $786万
-$24,547/呎
+$24,624/呎
 (24年-05月-06日)</t>
         </is>
       </c>
@@ -33194,17 +33194,17 @@
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $980万
-$22,016/呎
+$22,065/呎
 (21年-12月-07日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $785万
-$24,522/呎
+$24,599/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -33257,9 +33257,9 @@
       </c>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1102万
-$24,704/呎
+$24,760/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -33328,9 +33328,9 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1095万
-$24,556/呎
+$24,611/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -33344,9 +33344,9 @@
       </c>
       <c r="H32" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $781万
-$24,397/呎
+$24,473/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -33415,9 +33415,9 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $780万
-$24,375/呎
+$24,451/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -33470,9 +33470,9 @@
       </c>
       <c r="F34" s="21" t="inlineStr">
         <is>
-          <t>E | 446呎 (2房)
+          <t>E | 445呎 (2房)
 $1095万
-$24,545/呎
+$24,600/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -33486,9 +33486,9 @@
       </c>
       <c r="H34" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $779万
-$24,350/呎
+$24,426/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -33549,17 +33549,17 @@
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
-          <t>F | 445呎 (2房)
+          <t>F | 444呎 (2房)
 $1001万
-$22,499/呎
+$22,550/呎
 (21年-12月-14日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>G | 320呎 (1房)
+          <t>G | 319呎 (1房)
 $778万
-$24,322/呎
+$24,398/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -33745,9 +33745,9 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $906万
-$27,625/呎
+$27,541/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -33769,9 +33769,9 @@
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $847万
-$26,466/呎
+$26,549/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -33824,9 +33824,9 @@
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $876万
-$26,701/呎
+$26,620/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -33840,9 +33840,9 @@
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $842万
-$26,309/呎
+$26,392/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -33895,9 +33895,9 @@
       </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $898万
-$27,378/呎
+$27,295/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -33911,9 +33911,9 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $816万
-$25,506/呎
+$25,586/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -33958,17 +33958,17 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $895万
-$27,299/呎
+$27,216/呎
 (21年-12月-15日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $871万
-$26,543/呎
+$26,462/呎
 (21年-11月-18日)</t>
         </is>
       </c>
@@ -34037,9 +34037,9 @@
       </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $868万
-$26,463/呎
+$26,383/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -34100,17 +34100,17 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $865万
-$26,384/呎
+$26,304/呎
 (21年-12月-15日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $865万
-$26,384/呎
+$26,304/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -34124,9 +34124,9 @@
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $807万
-$25,228/呎
+$25,307/呎
 (21年-12月-06日)</t>
         </is>
       </c>
@@ -34179,9 +34179,9 @@
       </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $887万
-$27,052/呎
+$26,970/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -34321,9 +34321,9 @@
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $882万
-$26,893/呎
+$26,812/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -34408,9 +34408,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $822万
-$25,688/呎
+$25,768/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -34463,9 +34463,9 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $876万
-$26,716/呎
+$26,635/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -34479,9 +34479,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $815万
-$25,481/呎
+$25,561/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -34550,9 +34550,9 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $813万
-$25,403/呎
+$25,483/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -34621,9 +34621,9 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $788万
-$24,631/呎
+$24,708/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -34668,9 +34668,9 @@
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $844万
-$25,744/呎
+$25,666/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -34763,9 +34763,9 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $807万
-$25,228/呎
+$25,307/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -34881,9 +34881,9 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $837万
-$25,512/呎
+$25,435/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -34905,9 +34905,9 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $780万
-$24,384/呎
+$24,461/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -34952,9 +34952,9 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $834万
-$25,439/呎
+$25,362/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -35031,9 +35031,9 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $856万
-$26,082/呎
+$26,003/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -35118,9 +35118,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $791万
-$24,731/呎
+$24,809/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -35189,9 +35189,9 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $789万
-$24,653/呎
+$24,730/呎
 (21年-12月-07日)</t>
         </is>
       </c>
@@ -35244,9 +35244,9 @@
       </c>
       <c r="G26" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $847万
-$25,835/呎
+$25,757/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -35307,9 +35307,9 @@
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $859万
-$26,186/呎
+$26,106/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -35378,9 +35378,9 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $842万
-$25,680/呎
+$25,602/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -35520,9 +35520,9 @@
       </c>
       <c r="F30" s="21" t="inlineStr">
         <is>
-          <t>E | 328呎 (1房)
+          <t>E | 329呎 (1房)
 $837万
-$25,527/呎
+$25,450/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -35670,9 +35670,9 @@
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $830万
-$25,299/呎
+$25,222/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -35741,9 +35741,9 @@
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $827万
-$25,223/呎
+$25,146/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -35812,9 +35812,9 @@
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>F | 328呎 (1房)
+          <t>F | 329呎 (1房)
 $825万
-$25,149/呎
+$25,073/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -35828,9 +35828,9 @@
       </c>
       <c r="I34" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $758万
-$23,688/呎
+$23,762/呎
 (21年-12月-02日)</t>
         </is>
       </c>
@@ -35899,9 +35899,9 @@
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>H | 320呎 (1房)
+          <t>H | 319呎 (1房)
 $779万
-$24,334/呎
+$24,411/呎
 (21年-12月-02日)</t>
         </is>
       </c>
